--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\SimpleCodec\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D13F6A-3C43-4C96-8D59-5345A1102D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ED1EE5-EB02-4403-AE3B-2829F5301234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{9E0E118A-99EB-436F-AED0-9B6BC2E736B8}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>DSK24</t>
   </si>
   <si>
-    <t>C64890</t>
-  </si>
-  <si>
     <t>D3,D4,D5,D6</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,C13,C14,C22,C23,C38,C39,C40,C41,C42</t>
+  </si>
+  <si>
+    <t>C22466352</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3">
         <v>19</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -1389,7 +1389,7 @@
         <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -1397,27 +1397,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1429,75 +1429,75 @@
         <v>21</v>
       </c>
       <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
         <v>43</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>52</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>53</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14">
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
         <v>57</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1509,95 +1509,95 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
         <v>60</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
       </c>
       <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
         <v>64</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
         <v>68</v>
-      </c>
-      <c r="F17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
       </c>
       <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
         <v>72</v>
-      </c>
-      <c r="F18" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
       </c>
       <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
         <v>76</v>
-      </c>
-      <c r="F19" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1609,130 +1609,130 @@
         <v>21</v>
       </c>
       <c r="E20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" t="s">
         <v>79</v>
-      </c>
-      <c r="F20" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
         <v>82</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>83</v>
       </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
         <v>86</v>
       </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>87</v>
-      </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" t="s">
         <v>89</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>90</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>91</v>
-      </c>
-      <c r="F23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" t="s">
         <v>94</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>95</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>96</v>
-      </c>
-      <c r="F24" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
         <v>99</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>100</v>
       </c>
-      <c r="E25" t="s">
-        <v>101</v>
-      </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
         <v>103</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>104</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>105</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\PicoFX\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5098829A-A3A4-47F1-8D59-2D3A7F572B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D3E666-730C-4B87-82AC-90F7CA901001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{9E0E118A-99EB-436F-AED0-9B6BC2E736B8}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{9E0E118A-99EB-436F-AED0-9B6BC2E736B8}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
   <si>
     <t>Designator</t>
   </si>
@@ -180,9 +180,6 @@
     <t>HC-PM254-5.0H-2x8PS</t>
   </si>
   <si>
-    <t>R1,R25,R26,R27,R28,R29,R30</t>
-  </si>
-  <si>
     <t>47K</t>
   </si>
   <si>
@@ -192,18 +189,12 @@
     <t>0603WAF4702T5E</t>
   </si>
   <si>
-    <t>R2,R3,R4,R23,R24</t>
-  </si>
-  <si>
     <t>C22775</t>
   </si>
   <si>
     <t>0603WAF1000T5E</t>
   </si>
   <si>
-    <t>R5,R6,R7,R8</t>
-  </si>
-  <si>
     <t>1M</t>
   </si>
   <si>
@@ -213,9 +204,6 @@
     <t>0603WAF1004T5E</t>
   </si>
   <si>
-    <t>R9,R10</t>
-  </si>
-  <si>
     <t>1K</t>
   </si>
   <si>
@@ -225,9 +213,6 @@
     <t>0603WAF1001T5E</t>
   </si>
   <si>
-    <t>R11,R12,R13,R14</t>
-  </si>
-  <si>
     <t>15K</t>
   </si>
   <si>
@@ -237,9 +222,6 @@
     <t>0603WAF1502T5E</t>
   </si>
   <si>
-    <t>R15,R16,R21,R22</t>
-  </si>
-  <si>
     <t>11K</t>
   </si>
   <si>
@@ -249,9 +231,6 @@
     <t>0603WAF1102T5E</t>
   </si>
   <si>
-    <t>R17,R18,R19,R20</t>
-  </si>
-  <si>
     <t>C23253</t>
   </si>
   <si>
@@ -352,6 +331,36 @@
   </si>
   <si>
     <t>C31,C32,C40,C41</t>
+  </si>
+  <si>
+    <t>R1,R27,R28,R29,R30,R31,R32</t>
+  </si>
+  <si>
+    <t>R2,R5,R6,R25,R26</t>
+  </si>
+  <si>
+    <t>R3,R4</t>
+  </si>
+  <si>
+    <t>R7,R8,R9,R10</t>
+  </si>
+  <si>
+    <t>R11,R12</t>
+  </si>
+  <si>
+    <t>R13,R14,R15,R16</t>
+  </si>
+  <si>
+    <t>R17,R18,R23,R24</t>
+  </si>
+  <si>
+    <t>R19,R20,R21,R22</t>
+  </si>
+  <si>
+    <t>C22936</t>
+  </si>
+  <si>
+    <t>0603WAF100KT5E</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4CC479-4D6E-42CF-9375-451FBC777E4A}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1257,7 +1266,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B3">
         <v>19</v>
@@ -1277,7 +1286,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -1297,7 +1306,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -1317,7 +1326,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -1337,7 +1346,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -1389,7 +1398,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F9" t="s">
         <v>33</v>
@@ -1477,27 +1486,27 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="B14">
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" t="s">
         <v>53</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1509,230 +1518,250 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B16">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20">
-        <v>820</v>
+      <c r="C20" t="s">
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>820</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" t="s">
-        <v>102</v>
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\PicoFX\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D3E666-730C-4B87-82AC-90F7CA901001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F6ACD1E-640A-45FE-8916-A7BB4683F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{9E0E118A-99EB-436F-AED0-9B6BC2E736B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{32B43621-4DEF-4FAF-A1E0-7A727C6FC837}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="PicoFX" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,9 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
-  <si>
-    <t>Designator</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
+  <si>
+    <t>Reference</t>
   </si>
   <si>
     <t>Qty</t>
@@ -36,90 +36,78 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Footprint</t>
+    <t>Manufacturer Part</t>
   </si>
   <si>
     <t>JLCPCB Part</t>
   </si>
   <si>
-    <t>Manufacturer Part</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>RP_PICO_2</t>
-  </si>
-  <si>
-    <t>RP_PICO_2_SMD</t>
-  </si>
-  <si>
-    <t>C41407547</t>
-  </si>
-  <si>
-    <t>Pico 2</t>
+    <t>C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C17,C18,C26,C27,C42</t>
   </si>
   <si>
     <t>10u</t>
   </si>
   <si>
-    <t>0805_2012Metric</t>
+    <t>CL21A106KAYNNNE</t>
   </si>
   <si>
     <t>C15850</t>
   </si>
   <si>
-    <t>CL21A106KAYNNNE</t>
+    <t>C15,C16,C19,C20,C28,C29,C35,C39</t>
   </si>
   <si>
     <t>2.2n</t>
   </si>
   <si>
+    <t>CL21C222JBFNNNE</t>
+  </si>
+  <si>
     <t>C28260</t>
   </si>
   <si>
-    <t>CL21C222JBFNNNE</t>
+    <t>C21,C30,C33,C34,C36,C37,C38</t>
   </si>
   <si>
     <t>100n</t>
   </si>
   <si>
-    <t>0603_1608Metric</t>
+    <t>CC0603KRX7R9BB104</t>
   </si>
   <si>
     <t>C14663</t>
   </si>
   <si>
-    <t>CC0603KRX7R9BB104</t>
+    <t>C22,C23,C24,C25</t>
   </si>
   <si>
     <t>330p</t>
   </si>
   <si>
+    <t>CL10C331JB8NNNC</t>
+  </si>
+  <si>
     <t>C1664</t>
   </si>
   <si>
-    <t>CL10C331JB8NNNC</t>
+    <t>C31,C32,C40,C41</t>
   </si>
   <si>
     <t>1u</t>
   </si>
   <si>
+    <t>CL21B105KBFNNNE</t>
+  </si>
+  <si>
     <t>C28323</t>
   </si>
   <si>
-    <t>CL21B105KBFNNNE</t>
-  </si>
-  <si>
     <t>D1</t>
   </si>
   <si>
     <t>SMF10CA</t>
   </si>
   <si>
-    <t>SOD-123F</t>
-  </si>
-  <si>
     <t>C19077505</t>
   </si>
   <si>
@@ -129,112 +117,124 @@
     <t>DSK24</t>
   </si>
   <si>
+    <t>C22466352</t>
+  </si>
+  <si>
     <t>D3,D4,D5,D6</t>
   </si>
   <si>
     <t>H15VSD3B</t>
   </si>
   <si>
-    <t>SOD-323</t>
-  </si>
-  <si>
     <t>C20615814</t>
   </si>
   <si>
     <t>FB1,FB2,FB3</t>
   </si>
   <si>
+    <t>SDCL1608C68NJTDF</t>
+  </si>
+  <si>
     <t>C13415</t>
   </si>
   <si>
-    <t>SDCL1608C68NJTDF</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>RPI_ADC</t>
-  </si>
-  <si>
-    <t>HEADER_THROUGH_2x03_P2.54mm</t>
-  </si>
-  <si>
-    <t>C42163131</t>
-  </si>
-  <si>
-    <t>HC-PM254-5.0H-2x3PS-02A</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>RP_GPIO</t>
-  </si>
-  <si>
-    <t>HEADER_THROUGH_2x08_P2.54mm</t>
-  </si>
-  <si>
-    <t>C42163136</t>
-  </si>
-  <si>
-    <t>HC-PM254-5.0H-2x8PS</t>
+    <t>R1,R27,R28,R31,R32</t>
   </si>
   <si>
     <t>47K</t>
   </si>
   <si>
+    <t>0603WAF4702T5E</t>
+  </si>
+  <si>
     <t>C25819</t>
   </si>
   <si>
-    <t>0603WAF4702T5E</t>
+    <t>R2,R5,R6,R25,R26</t>
+  </si>
+  <si>
+    <t>0603WAF1000T5E</t>
   </si>
   <si>
     <t>C22775</t>
   </si>
   <si>
-    <t>0603WAF1000T5E</t>
+    <t>R3,R4</t>
+  </si>
+  <si>
+    <t>0603WAF100KT5E</t>
+  </si>
+  <si>
+    <t>C22936</t>
+  </si>
+  <si>
+    <t>R7,R8,R9,R10</t>
   </si>
   <si>
     <t>1M</t>
   </si>
   <si>
+    <t>0603WAF1004T5E</t>
+  </si>
+  <si>
     <t>C22935</t>
   </si>
   <si>
-    <t>0603WAF1004T5E</t>
+    <t>R11,R12</t>
   </si>
   <si>
     <t>1K</t>
   </si>
   <si>
+    <t>0603WAF1001T5E</t>
+  </si>
+  <si>
     <t>C21190</t>
   </si>
   <si>
-    <t>0603WAF1001T5E</t>
+    <t>R13,R14,R15,R16</t>
   </si>
   <si>
     <t>15K</t>
   </si>
   <si>
+    <t>0603WAF1502T5E</t>
+  </si>
+  <si>
     <t>C22809</t>
   </si>
   <si>
-    <t>0603WAF1502T5E</t>
+    <t>R17,R18,R23,R24</t>
   </si>
   <si>
     <t>11K</t>
   </si>
   <si>
+    <t>0603WAF1102T5E</t>
+  </si>
+  <si>
     <t>C25950</t>
   </si>
   <si>
-    <t>0603WAF1102T5E</t>
+    <t>R19,R20,R21,R22</t>
+  </si>
+  <si>
+    <t>0603WAF8200T5E</t>
   </si>
   <si>
     <t>C23253</t>
   </si>
   <si>
-    <t>0603WAF8200T5E</t>
+    <t>R29,R30</t>
+  </si>
+  <si>
+    <t>2.2K</t>
+  </si>
+  <si>
+    <t>0603WAF2201T5E</t>
+  </si>
+  <si>
+    <t>C4190</t>
   </si>
   <si>
     <t>U1</t>
@@ -243,9 +243,6 @@
     <t>AMS1117-5.0</t>
   </si>
   <si>
-    <t>SOT-223-3_TabPin2</t>
-  </si>
-  <si>
     <t>C6187</t>
   </si>
   <si>
@@ -264,103 +261,22 @@
     <t>MCP6002-xSN</t>
   </si>
   <si>
-    <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+    <t>MCP6002T-I/SN</t>
   </si>
   <si>
     <t>C7377</t>
   </si>
   <si>
-    <t>MCP6002T-I/SN</t>
-  </si>
-  <si>
     <t>U5</t>
   </si>
   <si>
     <t>CS4272</t>
   </si>
   <si>
-    <t>TSSOP-28_4.4x9.7mm_P0.65mm</t>
+    <t>CS4272-CZZR</t>
   </si>
   <si>
     <t>C2151111</t>
-  </si>
-  <si>
-    <t>CS4272-CZZR</t>
-  </si>
-  <si>
-    <t>X1-GUITAR</t>
-  </si>
-  <si>
-    <t>JACK_GUITAR</t>
-  </si>
-  <si>
-    <t>NMJ6HCD2</t>
-  </si>
-  <si>
-    <t>C368502</t>
-  </si>
-  <si>
-    <t>X1-DC</t>
-  </si>
-  <si>
-    <t>JACK_DC</t>
-  </si>
-  <si>
-    <t>BarrelJack_Horizontal</t>
-  </si>
-  <si>
-    <t>C319099</t>
-  </si>
-  <si>
-    <t>DC-005-2.5A-2.0</t>
-  </si>
-  <si>
-    <t>C22466352</t>
-  </si>
-  <si>
-    <t>C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C17,C18,C26,C27,C42</t>
-  </si>
-  <si>
-    <t>C15,C16,C19,C20,C28,C29,C35,C39</t>
-  </si>
-  <si>
-    <t>C21,C30,C33,C34,C36,C37,C38</t>
-  </si>
-  <si>
-    <t>C22,C23,C24,C25</t>
-  </si>
-  <si>
-    <t>C31,C32,C40,C41</t>
-  </si>
-  <si>
-    <t>R1,R27,R28,R29,R30,R31,R32</t>
-  </si>
-  <si>
-    <t>R2,R5,R6,R25,R26</t>
-  </si>
-  <si>
-    <t>R3,R4</t>
-  </si>
-  <si>
-    <t>R7,R8,R9,R10</t>
-  </si>
-  <si>
-    <t>R11,R12</t>
-  </si>
-  <si>
-    <t>R13,R14,R15,R16</t>
-  </si>
-  <si>
-    <t>R17,R18,R23,R24</t>
-  </si>
-  <si>
-    <t>R19,R20,R21,R22</t>
-  </si>
-  <si>
-    <t>C22936</t>
-  </si>
-  <si>
-    <t>0603WAF100KT5E</t>
   </si>
 </sst>
 </file>
@@ -1220,11 +1136,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4CC479-4D6E-42CF-9375-451FBC777E4A}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12581E9-D87F-4514-BD31-D9541CDC9AD3}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1240,76 +1156,64 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>99</v>
-      </c>
       <c r="B5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1320,13 +1224,10 @@
       <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>100</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -1335,36 +1236,30 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1375,393 +1270,265 @@
         <v>29</v>
       </c>
       <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>31</v>
       </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
       <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>850</v>
+      </c>
+      <c r="D10" t="s">
         <v>35</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>850</v>
-      </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>41</v>
       </c>
       <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="E13" t="s">
         <v>46</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>47</v>
       </c>
-      <c r="D13" t="s">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="F13" t="s">
+      <c r="E14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="F14" t="s">
+      <c r="D15" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
       </c>
       <c r="E15" t="s">
         <v>54</v>
       </c>
-      <c r="F15" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>104</v>
-      </c>
       <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>110</v>
-      </c>
-      <c r="F16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>820</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21">
-        <v>820</v>
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
         <v>83</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
